--- a/test-data/TestScema.xlsx
+++ b/test-data/TestScema.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bence\Desktop\SzoftverTechnologiák\se-lab4\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E35C3C9-3096-47C9-A904-0BC390AA286F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B70C4752-5B9C-4812-BF0A-4CC110CCF9B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D1D97A60-C7A2-42F2-9DF9-FBD004590D14}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="35">
   <si>
     <t>Tesztelt követelmény</t>
   </si>
@@ -159,9 +159,6 @@
     </r>
   </si>
   <si>
-    <t>a GT4500 torpedó vált, ha nincs valamelyikben.</t>
-  </si>
-  <si>
     <t>Az primary-ben kettő, a másikban nulla torpedó van.</t>
   </si>
   <si>
@@ -349,6 +346,103 @@
       </rPr>
       <t>SUCCESS; SUCCESS; FAIL</t>
     </r>
+  </si>
+  <si>
+    <t>a GT4500 torpedó vált, ha nincs valamelyikben. (2-&gt;1)</t>
+  </si>
+  <si>
+    <t>a GT4500 torpedó vált, ha nincs valamelyikben. (1 -&gt;2)</t>
+  </si>
+  <si>
+    <t>Az secondary-ban kettő, a másikban nulla torpedó van.</t>
+  </si>
+  <si>
+    <t>a GT4500 mindkét torpedójával egyszerre tüzelünk és a primary-ben nincs torpedó.</t>
+  </si>
+  <si>
+    <t>Secondary-ban van 1 torpedó.</t>
+  </si>
+  <si>
+    <r>
+      <t>a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="238"/>
+      </rPr>
+      <t>TORPEDO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t> parancs eredménye </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="238"/>
+      </rPr>
+      <t>FAIL</t>
+    </r>
+  </si>
+  <si>
+    <t>a GT4500 mindkét torpedójával egyszerre tüzelünk és a secondary-ben nincs torpedó.</t>
+  </si>
+  <si>
+    <t>Primary-ben van 1 torpedó.</t>
+  </si>
+  <si>
+    <r>
+      <t>a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="238"/>
+      </rPr>
+      <t>TORPEDO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t> parancs eredménye </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="238"/>
+      </rPr>
+      <t>SECCESS</t>
+    </r>
+  </si>
+  <si>
+    <t>Egyik tárolóban sincs torpedó.</t>
+  </si>
+  <si>
+    <t>a GT4500 mindkét torpedójával egyszerre tüzelünk, de egyikben sincs torpedó.</t>
   </si>
 </sst>
 </file>
@@ -791,9 +885,11 @@
     <col min="5" max="5" width="39.140625" customWidth="1"/>
     <col min="6" max="6" width="36.85546875" customWidth="1"/>
     <col min="7" max="7" width="41.140625" customWidth="1"/>
+    <col min="8" max="8" width="35.140625" customWidth="1"/>
+    <col min="9" max="9" width="35.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="55.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="88.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -801,24 +897,32 @@
         <v>8</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
+      <c r="I1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="L1" s="1"/>
     </row>
     <row r="2" spans="1:12" ht="54.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -829,24 +933,32 @@
         <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
+      <c r="I2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="L2" s="2"/>
     </row>
     <row r="3" spans="1:12" ht="63" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -854,27 +966,35 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
+      <c r="I3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="L3" s="1"/>
     </row>
     <row r="4" spans="1:12" ht="69" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -885,24 +1005,32 @@
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
+      <c r="I4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="L4" s="2"/>
     </row>
   </sheetData>

--- a/test-data/TestScema.xlsx
+++ b/test-data/TestScema.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bence\Desktop\SzoftverTechnologiák\se-lab4\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B70C4752-5B9C-4812-BF0A-4CC110CCF9B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4128B801-83E6-49B8-A3DF-43FAFD17B818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D1D97A60-C7A2-42F2-9DF9-FBD004590D14}"/>
   </bookViews>
@@ -887,6 +887,8 @@
     <col min="7" max="7" width="41.140625" customWidth="1"/>
     <col min="8" max="8" width="35.140625" customWidth="1"/>
     <col min="9" max="9" width="35.85546875" customWidth="1"/>
+    <col min="10" max="10" width="31.85546875" customWidth="1"/>
+    <col min="11" max="11" width="29" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="88.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
